--- a/Configs/奥术arcane.xlsx
+++ b/Configs/奥术arcane.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="34">
   <si>
     <t>id</t>
   </si>
@@ -71,6 +71,9 @@
     <t>bulletEvents</t>
   </si>
   <si>
+    <t>dragHint</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -95,6 +98,9 @@
     <t/>
   </si>
   <si>
+    <t>拖拽到目标区域释放</t>
+  </si>
+  <si>
     <t>寒冰术</t>
   </si>
   <si>
@@ -120,6 +126,9 @@
   </si>
   <si>
     <t>Icon/plant-64</t>
+  </si>
+  <si>
+    <t>拖拽到任意位置释放风暴</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1090,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="3" max="3" width="46.375" customWidth="1"/>
@@ -1091,7 +1100,7 @@
     <col min="14" max="14" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1134,63 +1143,69 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>4001</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>20000</v>
@@ -1214,27 +1229,30 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3">
         <v>70010</v>
       </c>
       <c r="N3" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>4002</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4">
         <v>20000</v>
@@ -1258,27 +1276,30 @@
         <v>2</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M4">
         <v>70201</v>
       </c>
       <c r="N4" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="O4" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4003</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>5000</v>
@@ -1302,27 +1323,30 @@
         <v>3</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5">
         <v>202003</v>
       </c>
+      <c r="O5" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4004</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>5000</v>
@@ -1346,13 +1370,16 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M6">
         <v>40002</v>
       </c>
       <c r="N6" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="O6" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/奥术arcane.xlsx
+++ b/Configs/奥术arcane.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>id</t>
   </si>
@@ -35,43 +35,34 @@
     <t>name</t>
   </si>
   <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>des</t>
   </si>
   <si>
-    <t>icon</t>
+    <t>upDes</t>
+  </si>
+  <si>
+    <t>levelDes</t>
   </si>
   <si>
     <t>dmg</t>
   </si>
   <si>
+    <t>upDmg</t>
+  </si>
+  <si>
     <t>dmgType</t>
   </si>
   <si>
-    <t>radius</t>
-  </si>
-  <si>
-    <t>tickInterval</t>
-  </si>
-  <si>
-    <t>cd</t>
-  </si>
-  <si>
     <t>runeCost</t>
   </si>
   <si>
     <t>runeType</t>
   </si>
   <si>
-    <t>events</t>
-  </si>
-  <si>
-    <t>enemyEvents</t>
-  </si>
-  <si>
-    <t>bulletEvents</t>
-  </si>
-  <si>
-    <t>dragHint</t>
+    <t>passives</t>
   </si>
   <si>
     <t>int</t>
@@ -80,55 +71,67 @@
     <t>string</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>陨石术</t>
-  </si>
-  <si>
-    <t>召唤陨石轰击指定区域，持续造成火焰伤害</t>
+    <t>{int level;string des}[]</t>
+  </si>
+  <si>
+    <t>{int level;int id}[]</t>
+  </si>
+  <si>
+    <t>狂热过载</t>
   </si>
   <si>
     <t>Icon/silver-ore-64</t>
   </si>
   <si>
+    <t>每次攻击有10%概率额外连射5枚过载弹，每颗造成20%火伤，该技能冷却1秒。</t>
+  </si>
+  <si>
+    <t>提升10%火伤</t>
+  </si>
+  <si>
+    <t>5~连射子弹变为10颗|10~触发概率提升至20%|20~连射的子弹会发生2次散射</t>
+  </si>
+  <si>
+    <t>1~4011|5~4012|10~4013|20~4014</t>
+  </si>
+  <si>
+    <t>缤纷雪球</t>
+  </si>
+  <si>
+    <t>子弹造成冰冻时，从该位置随机方向发射1颗雪球，每颗造成10%冰伤，并且有10%概率造成冰冻，持续1秒，该技能冷却1秒。</t>
+  </si>
+  <si>
+    <t>提升10%冰伤</t>
+  </si>
+  <si>
+    <t>5~随机发射3颗雪球|10~冰冻概率提升至30%|20~雪球命中时会发生小范围爆炸，造成10%冰伤，10%概率造成冰冻，持续1秒</t>
+  </si>
+  <si>
+    <t>霹雳弹闪</t>
+  </si>
+  <si>
+    <t>子弹造成伤害时，从该位置弹射出一枚闪电子弹攻击另一名敌人（如果没有找到敌人则弹射向随机位置），造成10%电伤，该技能冷却1秒。</t>
+  </si>
+  <si>
+    <t>提升10%电伤</t>
+  </si>
+  <si>
+    <t>5~闪电子弹增加3次弹射次数|10~发射5枚闪电子弹|20~每弹射一次伤害增加100%</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>拖拽到目标区域释放</t>
-  </si>
-  <si>
-    <t>寒冰术</t>
-  </si>
-  <si>
-    <t>在指定区域释放寒冰，造成冰霜伤害并冻结敌人2秒</t>
-  </si>
-  <si>
-    <t>Icon/sword-2-64</t>
-  </si>
-  <si>
-    <t>闪电网</t>
-  </si>
-  <si>
-    <t>在指定区域展开闪电网，造成雷电伤害并弹射3次</t>
-  </si>
-  <si>
-    <t>Icon/black-hole-64</t>
-  </si>
-  <si>
-    <t>风之诗</t>
-  </si>
-  <si>
-    <t>唤起全屏风暴，造成风属性伤害并击退敌人</t>
-  </si>
-  <si>
-    <t>Icon/plant-64</t>
-  </si>
-  <si>
-    <t>拖拽到任意位置释放风暴</t>
+    <t>风车之刃</t>
+  </si>
+  <si>
+    <t>自身100码内有敌人时，向前发射3枚跟踪风弹，每枚风弹造成10%风伤，并造成小距离击退，该技能冷却1秒。</t>
+  </si>
+  <si>
+    <t>提升10%风伤</t>
+  </si>
+  <si>
+    <t>5~向前发射10枚风弹|10~风弹命中后有50%概率分裂为两个更小的追踪风弹，造成一半的伤害|20~分裂风弹命中后会继续分裂两个更小的追踪风弹，造成一半的伤害</t>
   </si>
 </sst>
 </file>
@@ -141,13 +144,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -612,138 +621,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1090,33 +1108,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="3" max="3" width="46.375" customWidth="1"/>
-    <col min="4" max="4" width="20.375" customWidth="1"/>
-    <col min="8" max="8" width="13.75" customWidth="1"/>
-    <col min="13" max="13" width="12.625" customWidth="1"/>
-    <col min="14" max="14" width="13.75" customWidth="1"/>
+    <col min="3" max="3" width="20.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="47.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="49.125" customWidth="1"/>
+    <col min="12" max="12" width="32.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -1137,90 +1155,72 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+    <row r="3" ht="27" spans="1:12">
       <c r="A3">
         <v>4001</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3">
-        <v>20000</v>
-      </c>
-      <c r="F3">
+      <c r="G3">
+        <v>2000</v>
+      </c>
+      <c r="H3">
+        <v>1000</v>
+      </c>
+      <c r="I3">
         <v>1</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>30</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1229,45 +1229,36 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
-        <v>70010</v>
-      </c>
-      <c r="N3" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" ht="40.5" spans="1:12">
       <c r="A4">
         <v>4002</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4">
-        <v>20000</v>
-      </c>
-      <c r="F4">
+      <c r="G4">
+        <v>1000</v>
+      </c>
+      <c r="H4">
+        <v>1000</v>
+      </c>
+      <c r="I4">
         <v>2</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>30</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -1275,46 +1266,34 @@
       <c r="K4">
         <v>2</v>
       </c>
-      <c r="L4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4">
-        <v>70201</v>
-      </c>
-      <c r="N4" t="s">
-        <v>22</v>
-      </c>
-      <c r="O4" t="s">
-        <v>23</v>
-      </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" ht="40.5" spans="1:12">
       <c r="A5">
         <v>4003</v>
       </c>
       <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E5">
-        <v>5000</v>
-      </c>
-      <c r="F5">
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="H5">
+        <v>1000</v>
+      </c>
+      <c r="I5">
         <v>3</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>30</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -1323,45 +1302,36 @@
         <v>3</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5">
-        <v>202003</v>
-      </c>
-      <c r="O5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" ht="40.5" spans="1:12">
       <c r="A6">
         <v>4004</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E6">
-        <v>5000</v>
-      </c>
-      <c r="F6">
+      <c r="E6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <v>1000</v>
+      </c>
+      <c r="I6">
         <v>4</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>30</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -1370,16 +1340,7 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6">
-        <v>40002</v>
-      </c>
-      <c r="N6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
